--- a/data/robo_sensor_key_post08072025.xlsx
+++ b/data/robo_sensor_key_post08072025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10905"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/graceleuchtenberger/Library/Mobile Documents/com~apple~CloudDocs/Documents/Density_field/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2CCCBBFA-EFF0-0647-B94A-A7D53817D833}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A9FF601-C4B0-504B-A0DE-E0D6618AA4DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1360" yWindow="680" windowWidth="28040" windowHeight="17160" xr2:uid="{E5551131-2787-2048-A137-0E9CDA1D5CCA}"/>
+    <workbookView xWindow="5500" yWindow="880" windowWidth="28040" windowHeight="17160" xr2:uid="{E5551131-2787-2048-A137-0E9CDA1D5CCA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -586,7 +586,7 @@
         <v>94</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" t="s">
         <v>22</v>
@@ -678,7 +678,7 @@
         <v>97</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8" t="s">
         <v>22</v>
@@ -747,7 +747,7 @@
         <v>99</v>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11" t="s">
         <v>22</v>
@@ -793,7 +793,7 @@
         <v>27</v>
       </c>
       <c r="C13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" t="s">
         <v>22</v>
@@ -862,7 +862,7 @@
         <v>29</v>
       </c>
       <c r="C16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D16" t="s">
         <v>22</v>
@@ -954,7 +954,7 @@
         <v>44</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20" t="s">
         <v>22</v>
